--- a/forms/trg/Formulir_TRG_csva.xlsx
+++ b/forms/trg/Formulir_TRG_csva.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. Rusnadi Padjung</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -955,7 +959,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -996,7 +1000,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1041,7 +1045,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1078,7 +1082,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1119,7 +1123,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1160,7 +1164,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1201,7 +1205,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1234,7 +1238,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1267,7 +1271,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1300,7 +1304,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -1333,7 +1337,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1366,7 +1370,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1399,7 +1403,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1432,7 +1436,7 @@
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1465,7 +1469,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1473,7 +1477,11 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E20" s="11" t="n"/>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Cultivation technology in the 4.0 era requires smart agricultural concepts for increase the efficiency and effectiveness of cultivation. This concept can be done effectively if a data base is available in a morphophysiological approach and use of drones to assess vegetation indices. UAV drones can produces the corresponding Normalized Difference Vegetation Index algorithm with the greenness of the leaves, so this parameter can be associated with Leaf chlorophyll content for the photosynthesis process and productivity estimation plant.</t>
+        </is>
+      </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
@@ -1498,7 +1506,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
@@ -1543,7 +1551,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
@@ -1584,7 +1592,7 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
